--- a/public/modeles/modele-facture-sans-tva.xlsx
+++ b/public/modeles/modele-facture-sans-tva.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="60" formatCode="#  ##0.00"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -64,8 +65,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -526,28 +528,30 @@
       <c r="A24" t="str">
         <v>[Description de la prestation ou du produit]</v>
       </c>
-      <c r="B24" t="str">
+      <c r="B24">
         <v>1</v>
       </c>
-      <c r="C24" t="str">
-        <v>1 200,00</v>
-      </c>
-      <c r="D24">
-        <f>IF(B24="","",B24*C24)</f>
+      <c r="C24">
+        <v>1200</v>
+      </c>
+      <c r="D24" s="1">
+        <f>IF(B24="",0,B24*C24)</f>
+        <v>1200</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
         <v>[Deuxième ligne]</v>
       </c>
-      <c r="B25" t="str">
+      <c r="B25">
         <v>3</v>
       </c>
-      <c r="C25" t="str">
-        <v>100,00</v>
-      </c>
-      <c r="D25">
-        <f>IF(B25="","",B25*C25)</f>
+      <c r="C25">
+        <v>100</v>
+      </c>
+      <c r="D25" s="1">
+        <f>IF(B25="",0,B25*C25)</f>
+        <v>300</v>
       </c>
     </row>
     <row r="26">
@@ -560,16 +564,18 @@
       <c r="C26" t="str">
         <v/>
       </c>
-      <c r="D26">
-        <f>IF(B26="","",B26*C26)</f>
+      <c r="D26" s="1">
+        <f>IF(B26="",0,B26*C26)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
         <v>Total à payer</v>
       </c>
-      <c r="B28">
+      <c r="B28" s="1">
         <f>SUM(D24:D26)</f>
+        <v>1500</v>
       </c>
     </row>
     <row r="30">
@@ -594,7 +600,7 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>En cas de retard, pénalités au taux de [3 fois le taux d'intérêt légal] et indemnité forfaitaire pour frais de recouvrement de 40 €.</v>
+        <v>En cas de retard, pénalités au taux de [3 fois le taux d'intérêt légal] et indemnité forfaitaire pour frais de recouvrement de 40 euros.</v>
       </c>
     </row>
     <row r="36">

--- a/public/modeles/modele-facture-sans-tva.xlsx
+++ b/public/modeles/modele-facture-sans-tva.xlsx
@@ -425,7 +425,7 @@
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t xml:space="preserve">TVA non applicable, art. L. 223-3 du CIBS</t>
+          <t xml:space="preserve">TVA non applicable, art. 293 B du CGI</t>
         </is>
       </c>
     </row>
